--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0b2f4a5de066af7/Aplicaciones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_5AE51372516BE45EEA46B4955472A63A26896436" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_5AE51372516BE45EEA46B4955472A63A26896436" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7FED7B6-1EB1-4E9A-8E85-AE9C182F6AD8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -359,9 +359,6 @@
     <t>Tío Mario</t>
   </si>
   <si>
-    <t>TÍO MARIO; DIANA; JUAN DIEGO</t>
-  </si>
-  <si>
     <t>Tío Miguel</t>
   </si>
   <si>
@@ -378,6 +375,9 @@
   </si>
   <si>
     <t>YULIANA; MARTINA</t>
+  </si>
+  <si>
+    <t>TÍO MARIO; TÍA DIANA; PRIMO JUAN DIEGO</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1302,7 @@
         <v>107</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -1310,10 +1310,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" t="s">
         <v>109</v>
-      </c>
-      <c r="B54" t="s">
-        <v>110</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" t="s">
         <v>111</v>
-      </c>
-      <c r="B55" t="s">
-        <v>112</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56" t="s">
         <v>113</v>
-      </c>
-      <c r="B56" t="s">
-        <v>114</v>
       </c>
       <c r="C56">
         <v>2</v>

--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\USUARIO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizet\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C89696-2809-44D2-9FC8-522B317B7843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EEC6DF-8A57-4B45-8445-DE9F830E21C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invitados" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -127,12 +140,6 @@
     <t>ESTELLA</t>
   </si>
   <si>
-    <t>Esther</t>
-  </si>
-  <si>
-    <t>ESTHER; URIEL</t>
-  </si>
-  <si>
     <t>Fabian</t>
   </si>
   <si>
@@ -383,6 +390,12 @@
   </si>
   <si>
     <t>TÍO MARIO; TÍA DIANA;PRIMO JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>Abuela Esther</t>
+  </si>
+  <si>
+    <t>ABUELA ESTHER; ABUELO URIEL</t>
   </si>
 </sst>
 </file>
@@ -908,10 +921,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -919,10 +932,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -930,10 +943,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -941,10 +954,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -952,10 +965,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -963,10 +976,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -974,10 +987,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -985,10 +998,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -996,10 +1009,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1007,10 +1020,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1018,10 +1031,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -1029,10 +1042,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -1040,10 +1053,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1051,10 +1064,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -1062,10 +1075,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -1073,10 +1086,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -1084,10 +1097,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1095,10 +1108,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1106,10 +1119,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -1117,10 +1130,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1128,10 +1141,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1139,10 +1152,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1150,10 +1163,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1161,10 +1174,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -1172,10 +1185,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C41">
         <v>3</v>
@@ -1183,10 +1196,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -1194,10 +1207,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -1205,10 +1218,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1216,10 +1229,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1227,10 +1240,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -1238,10 +1251,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1249,10 +1262,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C48">
         <v>4</v>
@@ -1260,10 +1273,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1271,10 +1284,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -1282,10 +1295,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -1293,10 +1306,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -1304,10 +1317,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -1315,10 +1328,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -1326,10 +1339,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -1337,10 +1350,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C56">
         <v>3</v>
@@ -1348,10 +1361,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -1359,10 +1372,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -1370,10 +1383,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C59">
         <v>2</v>
